--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 01,10,26 лгрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 01,10,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B31CF5E-82DB-4F26-86AE-C7EEBF21208B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BF0A66-F233-4F65-B8EA-70FD39D65A29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$129</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="178">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -71,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -436,9 +441,6 @@
     <t xml:space="preserve"> 552  Ветчина Сливушка с индейкой ТМ Вязанка в модифицированной газовой среде 0,1 кг нарезка  ПОКОМ</t>
   </si>
   <si>
-    <t>15шт списано (24,08,26)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 553  Ассорти колбас Мясорубская коллекция: Сервелат Делюкс, С балыком 0,08 кг нарезка  ПОКОМ</t>
   </si>
   <si>
@@ -572,6 +574,15 @@
   <si>
     <t>нужно увеличить продажи / ПРОМ сентябрь (н+1)</t>
   </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>05,10,</t>
+  </si>
+  <si>
+    <t>нет в бланке / 15шт списано (24,08,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -623,7 +634,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,6 +675,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -700,7 +717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -719,6 +736,8 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1190,49 +1209,49 @@
         <v>15</v>
       </c>
       <c r="S3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AG3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
@@ -1261,49 +1280,51 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" s="1"/>
+      <c r="S4" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
@@ -1369,7 +1390,7 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>23087.148773250421</v>
+        <v>23067.148773250421</v>
       </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -1416,7 +1437,7 @@
       <c r="AF5" s="1"/>
       <c r="AG5" s="4">
         <f>SUM(AG6:AG500)</f>
-        <v>16860.966385210424</v>
+        <v>16860</v>
       </c>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -1431,10 +1452,10 @@
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C6" s="1">
         <v>4733.9549999999999</v>
@@ -1455,7 +1476,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1522,8 +1543,8 @@
       </c>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1">
-        <f>G6*S6</f>
-        <v>1682.0724425017988</v>
+        <f>ROUND(G6*S6,0)</f>
+        <v>1682</v>
       </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -1538,10 +1559,10 @@
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>1486.8969999999999</v>
@@ -1562,7 +1583,7 @@
         <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1629,8 +1650,8 @@
       </c>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1">
-        <f>G7*S7</f>
-        <v>442.68336799999997</v>
+        <f t="shared" ref="AG7:AG70" si="7">ROUND(G7*S7,0)</f>
+        <v>443</v>
       </c>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -1645,10 +1666,10 @@
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>2124.8690000000001</v>
@@ -1669,7 +1690,7 @@
         <v>45</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1736,8 +1757,8 @@
       </c>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1">
-        <f>G8*S8</f>
-        <v>739.82580844899985</v>
+        <f t="shared" si="7"/>
+        <v>740</v>
       </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -1752,10 +1773,10 @@
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -1766,7 +1787,7 @@
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -1827,9 +1848,12 @@
         <v>0</v>
       </c>
       <c r="AF9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG9" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1843,10 +1867,10 @@
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1">
         <v>1187</v>
@@ -1867,7 +1891,7 @@
         <v>45</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1891,7 +1915,7 @@
         <v>141.80000000000001</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" ref="S10:S12" si="7">11.5*R10-Q10-P10-O10-F10</f>
+        <f t="shared" ref="S10:S12" si="8">11.5*R10-Q10-P10-O10-F10</f>
         <v>485.11999999999989</v>
       </c>
       <c r="T10" s="1">
@@ -1934,8 +1958,8 @@
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1">
-        <f t="shared" ref="AG10:AG22" si="8">G10*S10</f>
-        <v>218.30399999999995</v>
+        <f t="shared" si="7"/>
+        <v>218</v>
       </c>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
@@ -1950,10 +1974,10 @@
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1">
         <v>1327.24</v>
@@ -1974,7 +1998,7 @@
         <v>45</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1998,7 +2022,7 @@
         <v>207.4</v>
       </c>
       <c r="S11" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>731.4139410000007</v>
       </c>
       <c r="T11" s="1">
@@ -2041,8 +2065,8 @@
       </c>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1">
-        <f t="shared" si="8"/>
-        <v>329.13627345000032</v>
+        <f t="shared" si="7"/>
+        <v>329</v>
       </c>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -2057,10 +2081,10 @@
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1">
         <v>164</v>
@@ -2081,7 +2105,7 @@
         <v>180</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -2105,7 +2129,7 @@
         <v>14.4</v>
       </c>
       <c r="S12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>32.799999999999983</v>
       </c>
       <c r="T12" s="1">
@@ -2148,8 +2172,8 @@
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1">
-        <f t="shared" si="8"/>
-        <v>5.5759999999999978</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
@@ -2164,10 +2188,10 @@
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1">
         <v>76</v>
@@ -2188,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -2252,7 +2276,7 @@
       </c>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH13" s="1"/>
@@ -2268,10 +2292,10 @@
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1">
         <v>448</v>
@@ -2292,7 +2316,7 @@
         <v>180</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -2359,8 +2383,8 @@
       </c>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1">
-        <f t="shared" si="8"/>
-        <v>25.312999999999999</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
@@ -2375,10 +2399,10 @@
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1">
         <v>865.79200000000003</v>
@@ -2399,7 +2423,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2423,7 +2447,7 @@
         <v>230.38240000000002</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" ref="S10:S22" si="9">12*R15-Q15-P15-O15-F15</f>
+        <f t="shared" ref="S15:S22" si="9">12*R15-Q15-P15-O15-F15</f>
         <v>668.67861220000032</v>
       </c>
       <c r="T15" s="1">
@@ -2466,8 +2490,8 @@
       </c>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1">
-        <f t="shared" si="8"/>
-        <v>668.67861220000032</v>
+        <f t="shared" si="7"/>
+        <v>669</v>
       </c>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
@@ -2482,10 +2506,10 @@
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1">
         <v>5376.1090000000004</v>
@@ -2506,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2571,8 +2595,8 @@
       </c>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1">
-        <f t="shared" si="8"/>
-        <v>612.04749918700145</v>
+        <f t="shared" si="7"/>
+        <v>612</v>
       </c>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
@@ -2587,10 +2611,10 @@
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1">
         <v>70.308999999999997</v>
@@ -2611,7 +2635,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -2675,7 +2699,7 @@
       </c>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH17" s="1"/>
@@ -2691,10 +2715,10 @@
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1">
         <v>98.869</v>
@@ -2715,7 +2739,7 @@
         <v>60</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -2779,7 +2803,7 @@
       </c>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH18" s="1"/>
@@ -2795,10 +2819,10 @@
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1">
         <v>17.492999999999999</v>
@@ -2819,7 +2843,7 @@
         <v>180</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -2883,7 +2907,7 @@
       </c>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH19" s="1"/>
@@ -2899,10 +2923,10 @@
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1">
         <v>1638.7619999999999</v>
@@ -2923,7 +2947,7 @@
         <v>60</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2990,8 +3014,8 @@
       </c>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1">
-        <f t="shared" si="8"/>
-        <v>367.07341963450426</v>
+        <f t="shared" si="7"/>
+        <v>367</v>
       </c>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
@@ -3006,10 +3030,10 @@
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1">
         <v>244.66300000000001</v>
@@ -3030,7 +3054,7 @@
         <v>70</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -3097,8 +3121,8 @@
       </c>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1">
-        <f t="shared" si="8"/>
-        <v>38.162620999999888</v>
+        <f t="shared" si="7"/>
+        <v>38</v>
       </c>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
@@ -3113,10 +3137,10 @@
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1">
         <v>900.35299999999995</v>
@@ -3137,7 +3161,7 @@
         <v>70</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -3203,11 +3227,11 @@
         <v>74.657200000000003</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG22" s="1">
-        <f t="shared" si="8"/>
-        <v>129.98589999999979</v>
+        <f t="shared" si="7"/>
+        <v>130</v>
       </c>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
@@ -3222,10 +3246,10 @@
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -3236,7 +3260,7 @@
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -3297,9 +3321,12 @@
         <v>0</v>
       </c>
       <c r="AF23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG23" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG23" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -3313,10 +3340,10 @@
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="1">
         <v>796.67700000000002</v>
@@ -3337,7 +3364,7 @@
         <v>70</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -3403,11 +3430,11 @@
         <v>119.8348</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" ref="AG24:AG29" si="12">G24*S24</f>
-        <v>102.02601000000016</v>
+        <f t="shared" si="7"/>
+        <v>102</v>
       </c>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
@@ -3422,10 +3449,10 @@
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1">
         <v>263.92</v>
@@ -3446,7 +3473,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -3513,8 +3540,8 @@
       </c>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1">
-        <f t="shared" si="12"/>
-        <v>66.932840000000027</v>
+        <f t="shared" si="7"/>
+        <v>67</v>
       </c>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
@@ -3529,10 +3556,10 @@
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1">
         <v>51.814999999999998</v>
@@ -3553,7 +3580,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -3620,8 +3647,8 @@
       </c>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1">
-        <f t="shared" si="12"/>
-        <v>9.8638000000000829</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
@@ -3636,10 +3663,10 @@
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" s="1">
         <v>75.147999999999996</v>
@@ -3660,7 +3687,7 @@
         <v>40</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -3727,8 +3754,8 @@
       </c>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1">
-        <f t="shared" si="12"/>
-        <v>74.887299999999925</v>
+        <f t="shared" si="7"/>
+        <v>75</v>
       </c>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
@@ -3743,10 +3770,10 @@
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
         <v>1632.039</v>
@@ -3767,7 +3794,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -3834,8 +3861,8 @@
       </c>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1">
-        <f t="shared" si="12"/>
-        <v>820.72705999999994</v>
+        <f t="shared" si="7"/>
+        <v>821</v>
       </c>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
@@ -3850,10 +3877,10 @@
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
         <v>2042.452</v>
@@ -3874,7 +3901,7 @@
         <v>40</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
@@ -3941,8 +3968,8 @@
       </c>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1">
-        <f t="shared" si="12"/>
-        <v>984.1034499999987</v>
+        <f t="shared" si="7"/>
+        <v>984</v>
       </c>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -3957,10 +3984,10 @@
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -3971,7 +3998,7 @@
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
@@ -4032,9 +4059,12 @@
         <v>0</v>
       </c>
       <c r="AF30" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG30" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG30" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
@@ -4048,10 +4078,10 @@
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1">
         <v>80.528000000000006</v>
@@ -4072,7 +4102,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
@@ -4139,8 +4169,8 @@
       </c>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1">
-        <f>G31*S31</f>
-        <v>89.9591309999998</v>
+        <f t="shared" si="7"/>
+        <v>90</v>
       </c>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
@@ -4155,10 +4185,10 @@
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -4169,7 +4199,7 @@
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
@@ -4230,9 +4260,12 @@
         <v>0</v>
       </c>
       <c r="AF32" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG32" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG32" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
@@ -4246,10 +4279,10 @@
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -4260,7 +4293,7 @@
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
@@ -4321,9 +4354,12 @@
         <v>0</v>
       </c>
       <c r="AF33" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG33" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG33" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -4337,10 +4373,10 @@
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1">
         <v>3725</v>
@@ -4361,7 +4397,7 @@
         <v>45</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -4385,7 +4421,7 @@
         <v>986.06000000000006</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" ref="S34:S84" si="13">12*R34-Q34-P34-O34-F34</f>
+        <f t="shared" ref="S34:S73" si="12">12*R34-Q34-P34-O34-F34</f>
         <v>2878.478000000001</v>
       </c>
       <c r="T34" s="1">
@@ -4428,8 +4464,8 @@
       </c>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1">
-        <f t="shared" ref="AG34:AG65" si="14">G34*S34</f>
-        <v>1151.3912000000005</v>
+        <f t="shared" si="7"/>
+        <v>1151</v>
       </c>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
@@ -4444,10 +4480,10 @@
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1">
         <v>947</v>
@@ -4468,7 +4504,7 @@
         <v>50</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -4535,8 +4571,8 @@
       </c>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1">
-        <f t="shared" si="14"/>
-        <v>143.86804694999989</v>
+        <f t="shared" si="7"/>
+        <v>144</v>
       </c>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
@@ -4551,10 +4587,10 @@
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1">
         <v>1296</v>
@@ -4575,7 +4611,7 @@
         <v>45</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -4599,7 +4635,7 @@
         <v>197.4</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1066.9099999999999</v>
       </c>
       <c r="T36" s="1">
@@ -4642,8 +4678,8 @@
       </c>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1">
-        <f t="shared" si="14"/>
-        <v>426.76399999999995</v>
+        <f t="shared" si="7"/>
+        <v>427</v>
       </c>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
@@ -4658,10 +4694,10 @@
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1">
         <v>22</v>
@@ -4682,7 +4718,7 @@
         <v>40</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4706,7 +4742,7 @@
         <v>3.6</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>9.2000000000000028</v>
       </c>
       <c r="T37" s="1">
@@ -4749,8 +4785,8 @@
       </c>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1">
-        <f t="shared" si="14"/>
-        <v>3.6800000000000015</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
@@ -4765,10 +4801,10 @@
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1">
         <v>204.43700000000001</v>
@@ -4789,14 +4825,14 @@
         <v>45</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>112.8</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>4.2660000000000053</v>
       </c>
       <c r="M38" s="1"/>
@@ -4809,19 +4845,19 @@
         <v>44.013900000000064</v>
       </c>
       <c r="R38" s="1">
-        <f t="shared" ref="R38:R69" si="16">E38/5</f>
+        <f t="shared" ref="R38:R69" si="14">E38/5</f>
         <v>23.4132</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>72.092699999999965</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" ref="T38:T69" si="17">(F38+O38+P38+Q38+S38)/R38</f>
+        <f t="shared" ref="T38:T69" si="15">(F38+O38+P38+Q38+S38)/R38</f>
         <v>12</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="18">(F38+O38+P38+Q38)/R38</f>
+        <f t="shared" ref="U38:U69" si="16">(F38+O38+P38+Q38)/R38</f>
         <v>8.9208523397058084</v>
       </c>
       <c r="V38" s="1">
@@ -4856,8 +4892,8 @@
       </c>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1">
-        <f t="shared" si="14"/>
-        <v>72.092699999999965</v>
+        <f t="shared" si="7"/>
+        <v>72</v>
       </c>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
@@ -4872,10 +4908,10 @@
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="1">
         <v>748</v>
@@ -4896,14 +4932,14 @@
         <v>731</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
         <v>389</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M39" s="1"/>
@@ -4916,7 +4952,7 @@
         <v>155.07500000000019</v>
       </c>
       <c r="R39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>76.599999999999994</v>
       </c>
       <c r="S39" s="5">
@@ -4924,11 +4960,11 @@
         <v>95.699999999999932</v>
       </c>
       <c r="T39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>11.5</v>
       </c>
       <c r="U39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>10.250652741514362</v>
       </c>
       <c r="V39" s="1">
@@ -4963,8 +4999,8 @@
       </c>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1">
-        <f t="shared" si="14"/>
-        <v>9.5699999999999932</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
@@ -4979,10 +5015,10 @@
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="1">
         <v>18</v>
@@ -5003,14 +5039,14 @@
         <v>40</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>294</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-133</v>
       </c>
       <c r="M40" s="1"/>
@@ -5023,18 +5059,18 @@
         <v>50</v>
       </c>
       <c r="R40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>32.200000000000003</v>
       </c>
       <c r="S40" s="5">
         <v>200</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>8.0434782608695645</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1.8322981366459625</v>
       </c>
       <c r="V40" s="1">
@@ -5069,7 +5105,7 @@
       </c>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>70</v>
       </c>
       <c r="AH40" s="1"/>
@@ -5085,10 +5121,10 @@
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="1">
         <v>1.149</v>
@@ -5109,14 +5145,14 @@
         <v>40</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1">
         <v>91.7</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-27.962000000000003</v>
       </c>
       <c r="M41" s="1"/>
@@ -5129,19 +5165,19 @@
         <v>0</v>
       </c>
       <c r="R41" s="1">
+        <f t="shared" si="14"/>
+        <v>12.7476</v>
+      </c>
+      <c r="S41" s="5">
+        <f t="shared" si="12"/>
+        <v>24.595299999999995</v>
+      </c>
+      <c r="T41" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U41" s="1">
         <f t="shared" si="16"/>
-        <v>12.7476</v>
-      </c>
-      <c r="S41" s="5">
-        <f t="shared" si="13"/>
-        <v>24.595299999999995</v>
-      </c>
-      <c r="T41" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U41" s="1">
-        <f t="shared" si="18"/>
         <v>10.070593680379051</v>
       </c>
       <c r="V41" s="1">
@@ -5176,8 +5212,8 @@
       </c>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1">
-        <f t="shared" si="14"/>
-        <v>24.595299999999995</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
@@ -5192,10 +5228,10 @@
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1">
         <v>782</v>
@@ -5216,14 +5252,14 @@
         <v>40</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
         <v>501</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M42" s="1"/>
@@ -5236,19 +5272,19 @@
         <v>80.709999999999965</v>
       </c>
       <c r="R42" s="1">
+        <f t="shared" si="14"/>
+        <v>99.6</v>
+      </c>
+      <c r="S42" s="5">
+        <f t="shared" si="12"/>
+        <v>192.78999999999974</v>
+      </c>
+      <c r="T42" s="1">
+        <f t="shared" si="15"/>
+        <v>11.999999999999998</v>
+      </c>
+      <c r="U42" s="1">
         <f t="shared" si="16"/>
-        <v>99.6</v>
-      </c>
-      <c r="S42" s="5">
-        <f t="shared" si="13"/>
-        <v>192.78999999999974</v>
-      </c>
-      <c r="T42" s="1">
-        <f t="shared" si="17"/>
-        <v>11.999999999999998</v>
-      </c>
-      <c r="U42" s="1">
-        <f t="shared" si="18"/>
         <v>10.064357429718875</v>
       </c>
       <c r="V42" s="1">
@@ -5283,8 +5319,8 @@
       </c>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1">
-        <f t="shared" si="14"/>
-        <v>77.1159999999999</v>
+        <f t="shared" si="7"/>
+        <v>77</v>
       </c>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
@@ -5299,10 +5335,10 @@
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1">
         <v>123</v>
@@ -5323,14 +5359,14 @@
         <v>45</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1">
         <v>318</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-149</v>
       </c>
       <c r="M43" s="1"/>
@@ -5343,18 +5379,18 @@
         <v>50</v>
       </c>
       <c r="R43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33.799999999999997</v>
       </c>
       <c r="S43" s="5">
         <v>100</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>17.390532544378701</v>
       </c>
       <c r="U43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>14.431952662721896</v>
       </c>
       <c r="V43" s="1">
@@ -5389,7 +5425,7 @@
       </c>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="AH43" s="1"/>
@@ -5405,10 +5441,10 @@
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C44" s="1">
         <v>0.93700000000000006</v>
@@ -5429,14 +5465,14 @@
         <v>40</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1">
         <v>276.45</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-28.695999999999998</v>
       </c>
       <c r="M44" s="1"/>
@@ -5449,19 +5485,19 @@
         <v>0</v>
       </c>
       <c r="R44" s="1">
+        <f t="shared" si="14"/>
+        <v>49.550799999999995</v>
+      </c>
+      <c r="S44" s="5">
+        <f t="shared" si="12"/>
+        <v>118.8476</v>
+      </c>
+      <c r="T44" s="1">
+        <f t="shared" si="15"/>
+        <v>12.000000000000002</v>
+      </c>
+      <c r="U44" s="1">
         <f t="shared" si="16"/>
-        <v>49.550799999999995</v>
-      </c>
-      <c r="S44" s="5">
-        <f t="shared" si="13"/>
-        <v>118.8476</v>
-      </c>
-      <c r="T44" s="1">
-        <f t="shared" si="17"/>
-        <v>12.000000000000002</v>
-      </c>
-      <c r="U44" s="1">
-        <f t="shared" si="18"/>
         <v>9.601499874875886</v>
       </c>
       <c r="V44" s="1">
@@ -5496,8 +5532,8 @@
       </c>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1">
-        <f t="shared" si="14"/>
-        <v>118.8476</v>
+        <f t="shared" si="7"/>
+        <v>119</v>
       </c>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
@@ -5512,10 +5548,10 @@
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="1">
         <v>18</v>
@@ -5536,14 +5572,14 @@
         <v>40</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1">
         <v>1051</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-518</v>
       </c>
       <c r="M45" s="1"/>
@@ -5556,18 +5592,18 @@
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>106.6</v>
       </c>
       <c r="S45" s="5">
         <v>800</v>
       </c>
       <c r="T45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>10.909943714821765</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>3.4052532833020641</v>
       </c>
       <c r="V45" s="1">
@@ -5602,7 +5638,7 @@
       </c>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>280</v>
       </c>
       <c r="AH45" s="1"/>
@@ -5618,10 +5654,10 @@
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="1">
         <v>584</v>
@@ -5642,14 +5678,14 @@
         <v>40</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1">
         <v>605</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-65</v>
       </c>
       <c r="M46" s="1"/>
@@ -5662,19 +5698,19 @@
         <v>84</v>
       </c>
       <c r="R46" s="1">
+        <f t="shared" si="14"/>
+        <v>108</v>
+      </c>
+      <c r="S46" s="5">
+        <f t="shared" si="12"/>
+        <v>81.899999999999864</v>
+      </c>
+      <c r="T46" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U46" s="1">
         <f t="shared" si="16"/>
-        <v>108</v>
-      </c>
-      <c r="S46" s="5">
-        <f t="shared" si="13"/>
-        <v>81.899999999999864</v>
-      </c>
-      <c r="T46" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U46" s="1">
-        <f t="shared" si="18"/>
         <v>11.241666666666667</v>
       </c>
       <c r="V46" s="1">
@@ -5709,8 +5745,8 @@
       </c>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1">
-        <f t="shared" si="14"/>
-        <v>32.759999999999948</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
@@ -5725,10 +5761,10 @@
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1">
         <v>570.59199999999998</v>
@@ -5749,14 +5785,14 @@
         <v>50</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1">
         <v>419.5</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>3.910000000000025</v>
       </c>
       <c r="M47" s="1"/>
@@ -5769,19 +5805,19 @@
         <v>323.74856339999991</v>
       </c>
       <c r="R47" s="1">
+        <f t="shared" si="14"/>
+        <v>84.682000000000002</v>
+      </c>
+      <c r="S47" s="5">
+        <f t="shared" ref="S47:S48" si="17">11.5*R47-Q47-P47-O47-F47</f>
+        <v>102.000730793</v>
+      </c>
+      <c r="T47" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U47" s="1">
         <f t="shared" si="16"/>
-        <v>84.682000000000002</v>
-      </c>
-      <c r="S47" s="5">
-        <f t="shared" ref="S47:S48" si="19">11.5*R47-Q47-P47-O47-F47</f>
-        <v>102.000730793</v>
-      </c>
-      <c r="T47" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U47" s="1">
-        <f t="shared" si="18"/>
         <v>10.295485099631563</v>
       </c>
       <c r="V47" s="1">
@@ -5816,8 +5852,8 @@
       </c>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1">
-        <f t="shared" si="14"/>
-        <v>102.000730793</v>
+        <f t="shared" si="7"/>
+        <v>102</v>
       </c>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
@@ -5832,10 +5868,10 @@
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
         <v>787.34900000000005</v>
@@ -5856,14 +5892,14 @@
         <v>50</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1">
         <v>629.25</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-46.182000000000016</v>
       </c>
       <c r="M48" s="1"/>
@@ -5876,19 +5912,19 @@
         <v>45.255030999999803</v>
       </c>
       <c r="R48" s="1">
+        <f t="shared" si="14"/>
+        <v>116.61359999999999</v>
+      </c>
+      <c r="S48" s="5">
+        <f t="shared" si="17"/>
+        <v>223.07807731700052</v>
+      </c>
+      <c r="T48" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U48" s="1">
         <f t="shared" si="16"/>
-        <v>116.61359999999999</v>
-      </c>
-      <c r="S48" s="5">
-        <f t="shared" si="19"/>
-        <v>223.07807731700052</v>
-      </c>
-      <c r="T48" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U48" s="1">
-        <f t="shared" si="18"/>
         <v>9.5870320672974643</v>
       </c>
       <c r="V48" s="1">
@@ -5923,8 +5959,8 @@
       </c>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1">
-        <f t="shared" si="14"/>
-        <v>223.07807731700052</v>
+        <f t="shared" si="7"/>
+        <v>223</v>
       </c>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
@@ -5939,10 +5975,10 @@
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1">
         <v>17.664000000000001</v>
@@ -5963,14 +5999,14 @@
         <v>45</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1">
         <v>1.3</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.19500000000000006</v>
       </c>
       <c r="M49" s="1"/>
@@ -5983,16 +6019,16 @@
         <v>0</v>
       </c>
       <c r="R49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.29900000000000004</v>
       </c>
       <c r="S49" s="5"/>
       <c r="T49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>115.0735785953177</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>115.0735785953177</v>
       </c>
       <c r="V49" s="1">
@@ -6026,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="AF49" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH49" s="1"/>
@@ -6045,10 +6081,10 @@
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="1">
         <v>192</v>
@@ -6069,14 +6105,14 @@
         <v>50</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1">
         <v>193</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-8</v>
       </c>
       <c r="M50" s="1"/>
@@ -6089,19 +6125,19 @@
         <v>0</v>
       </c>
       <c r="R50" s="1">
+        <f t="shared" si="14"/>
+        <v>37</v>
+      </c>
+      <c r="S50" s="5">
+        <f t="shared" ref="S50:S51" si="18">11.5*R50-Q50-P50-O50-F50</f>
+        <v>118.5</v>
+      </c>
+      <c r="T50" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U50" s="1">
         <f t="shared" si="16"/>
-        <v>37</v>
-      </c>
-      <c r="S50" s="5">
-        <f t="shared" ref="S50:S51" si="20">11.5*R50-Q50-P50-O50-F50</f>
-        <v>118.5</v>
-      </c>
-      <c r="T50" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U50" s="1">
-        <f t="shared" si="18"/>
         <v>8.2972972972972965</v>
       </c>
       <c r="V50" s="1">
@@ -6136,8 +6172,8 @@
       </c>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1">
-        <f t="shared" si="14"/>
-        <v>53.325000000000003</v>
+        <f t="shared" si="7"/>
+        <v>53</v>
       </c>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
@@ -6152,10 +6188,10 @@
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="1">
         <v>592</v>
@@ -6176,14 +6212,14 @@
         <v>50</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1">
         <v>499</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M51" s="1"/>
@@ -6196,19 +6232,19 @@
         <v>94.045999999999822</v>
       </c>
       <c r="R51" s="1">
+        <f t="shared" si="14"/>
+        <v>99.2</v>
+      </c>
+      <c r="S51" s="5">
+        <f t="shared" si="18"/>
+        <v>236.25399999999991</v>
+      </c>
+      <c r="T51" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U51" s="1">
         <f t="shared" si="16"/>
-        <v>99.2</v>
-      </c>
-      <c r="S51" s="5">
-        <f t="shared" si="20"/>
-        <v>236.25399999999991</v>
-      </c>
-      <c r="T51" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U51" s="1">
-        <f t="shared" si="18"/>
         <v>9.1184072580645168</v>
       </c>
       <c r="V51" s="1">
@@ -6243,8 +6279,8 @@
       </c>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1">
-        <f t="shared" si="14"/>
-        <v>106.31429999999996</v>
+        <f t="shared" si="7"/>
+        <v>106</v>
       </c>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
@@ -6259,10 +6295,10 @@
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="1">
         <v>108</v>
@@ -6281,14 +6317,14 @@
         <v>40</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1">
         <v>45</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-14</v>
       </c>
       <c r="M52" s="1"/>
@@ -6301,16 +6337,16 @@
         <v>15.19999999999999</v>
       </c>
       <c r="R52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>6.2</v>
       </c>
       <c r="S52" s="5"/>
       <c r="T52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>12.774193548387094</v>
       </c>
       <c r="U52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>12.774193548387094</v>
       </c>
       <c r="V52" s="1">
@@ -6345,7 +6381,7 @@
       </c>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH52" s="1"/>
@@ -6361,10 +6397,10 @@
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="1">
         <v>86</v>
@@ -6385,14 +6421,14 @@
         <v>40</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1">
         <v>83</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M53" s="1"/>
@@ -6405,19 +6441,19 @@
         <v>0</v>
       </c>
       <c r="R53" s="1">
+        <f t="shared" si="14"/>
+        <v>15.8</v>
+      </c>
+      <c r="S53" s="5">
+        <f t="shared" si="12"/>
+        <v>17.40000000000002</v>
+      </c>
+      <c r="T53" s="1">
+        <f t="shared" si="15"/>
+        <v>12.000000000000002</v>
+      </c>
+      <c r="U53" s="1">
         <f t="shared" si="16"/>
-        <v>15.8</v>
-      </c>
-      <c r="S53" s="5">
-        <f t="shared" si="13"/>
-        <v>17.40000000000002</v>
-      </c>
-      <c r="T53" s="1">
-        <f t="shared" si="17"/>
-        <v>12.000000000000002</v>
-      </c>
-      <c r="U53" s="1">
-        <f t="shared" si="18"/>
         <v>10.898734177215189</v>
       </c>
       <c r="V53" s="1">
@@ -6452,8 +6488,8 @@
       </c>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1">
-        <f t="shared" si="14"/>
-        <v>6.960000000000008</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
@@ -6468,10 +6504,10 @@
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1">
         <v>900.15</v>
@@ -6492,14 +6528,14 @@
         <v>50</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1">
         <v>604.9</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>14.02800000000002</v>
       </c>
       <c r="M54" s="1"/>
@@ -6512,19 +6548,19 @@
         <v>184.94293799999991</v>
       </c>
       <c r="R54" s="1">
+        <f t="shared" si="14"/>
+        <v>123.7856</v>
+      </c>
+      <c r="S54" s="5">
+        <f t="shared" ref="S54:S59" si="19">11.5*R54-Q54-P54-O54-F54</f>
+        <v>146.06286200000011</v>
+      </c>
+      <c r="T54" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U54" s="1">
         <f t="shared" si="16"/>
-        <v>123.7856</v>
-      </c>
-      <c r="S54" s="5">
-        <f t="shared" ref="S54:S59" si="21">11.5*R54-Q54-P54-O54-F54</f>
-        <v>146.06286200000011</v>
-      </c>
-      <c r="T54" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U54" s="1">
-        <f t="shared" si="18"/>
         <v>10.32003349339503</v>
       </c>
       <c r="V54" s="1">
@@ -6559,8 +6595,8 @@
       </c>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1">
-        <f t="shared" si="14"/>
-        <v>146.06286200000011</v>
+        <f t="shared" si="7"/>
+        <v>146</v>
       </c>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
@@ -6575,10 +6611,10 @@
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="1">
         <v>581</v>
@@ -6601,14 +6637,14 @@
         <v>731</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1">
         <v>242</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>97</v>
       </c>
       <c r="M55" s="1"/>
@@ -6621,19 +6657,19 @@
         <v>128.76599999999999</v>
       </c>
       <c r="R55" s="1">
+        <f t="shared" si="14"/>
+        <v>67.8</v>
+      </c>
+      <c r="S55" s="5">
+        <f t="shared" si="19"/>
+        <v>79.899999999999977</v>
+      </c>
+      <c r="T55" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U55" s="1">
         <f t="shared" si="16"/>
-        <v>67.8</v>
-      </c>
-      <c r="S55" s="5">
-        <f t="shared" si="21"/>
-        <v>79.899999999999977</v>
-      </c>
-      <c r="T55" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U55" s="1">
-        <f t="shared" si="18"/>
         <v>10.321533923303834</v>
       </c>
       <c r="V55" s="1">
@@ -6668,8 +6704,8 @@
       </c>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1">
-        <f t="shared" si="14"/>
-        <v>7.9899999999999984</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
@@ -6684,10 +6720,10 @@
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1">
         <v>1166.345</v>
@@ -6708,14 +6744,14 @@
         <v>50</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1">
         <v>910.33</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>3.7729999999999109</v>
       </c>
       <c r="M56" s="1"/>
@@ -6728,19 +6764,19 @@
         <v>307.34785539999979</v>
       </c>
       <c r="R56" s="1">
+        <f t="shared" si="14"/>
+        <v>182.82059999999998</v>
+      </c>
+      <c r="S56" s="5">
+        <f t="shared" si="19"/>
+        <v>478.43406910979979</v>
+      </c>
+      <c r="T56" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U56" s="1">
         <f t="shared" si="16"/>
-        <v>182.82059999999998</v>
-      </c>
-      <c r="S56" s="5">
-        <f t="shared" si="21"/>
-        <v>478.43406910979979</v>
-      </c>
-      <c r="T56" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U56" s="1">
-        <f t="shared" si="18"/>
         <v>8.8830407015959914</v>
       </c>
       <c r="V56" s="1">
@@ -6775,8 +6811,8 @@
       </c>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1">
-        <f t="shared" si="14"/>
-        <v>478.43406910979979</v>
+        <f t="shared" si="7"/>
+        <v>478</v>
       </c>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
@@ -6791,10 +6827,10 @@
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57" s="1">
         <v>97.081000000000003</v>
@@ -6815,14 +6851,14 @@
         <v>55</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1">
         <v>65.8</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2.3239999999999981</v>
       </c>
       <c r="M57" s="1"/>
@@ -6835,19 +6871,19 @@
         <v>0</v>
       </c>
       <c r="R57" s="1">
+        <f t="shared" si="14"/>
+        <v>13.624799999999999</v>
+      </c>
+      <c r="S57" s="5">
+        <f t="shared" si="19"/>
+        <v>8.6851999999999805</v>
+      </c>
+      <c r="T57" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U57" s="1">
         <f t="shared" si="16"/>
-        <v>13.624799999999999</v>
-      </c>
-      <c r="S57" s="5">
-        <f t="shared" si="21"/>
-        <v>8.6851999999999805</v>
-      </c>
-      <c r="T57" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U57" s="1">
-        <f t="shared" si="18"/>
         <v>10.862544771299396</v>
       </c>
       <c r="V57" s="1">
@@ -6882,8 +6918,8 @@
       </c>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1">
-        <f t="shared" si="14"/>
-        <v>8.6851999999999805</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
@@ -6898,10 +6934,10 @@
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="1">
         <v>439</v>
@@ -6922,14 +6958,14 @@
         <v>731</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1">
         <v>200</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M58" s="1"/>
@@ -6942,19 +6978,19 @@
         <v>71.600000000000023</v>
       </c>
       <c r="R58" s="1">
+        <f t="shared" si="14"/>
+        <v>40.200000000000003</v>
+      </c>
+      <c r="S58" s="5">
+        <f t="shared" si="19"/>
+        <v>117.69999999999999</v>
+      </c>
+      <c r="T58" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U58" s="1">
         <f t="shared" si="16"/>
-        <v>40.200000000000003</v>
-      </c>
-      <c r="S58" s="5">
-        <f t="shared" si="21"/>
-        <v>117.69999999999999</v>
-      </c>
-      <c r="T58" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U58" s="1">
-        <f t="shared" si="18"/>
         <v>8.5721393034825866</v>
       </c>
       <c r="V58" s="1">
@@ -6989,8 +7025,8 @@
       </c>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1">
-        <f t="shared" si="14"/>
-        <v>11.77</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
@@ -7005,10 +7041,10 @@
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="1">
         <v>268</v>
@@ -7029,14 +7065,14 @@
         <v>50</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1">
         <v>252</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-17</v>
       </c>
       <c r="M59" s="1"/>
@@ -7049,19 +7085,19 @@
         <v>308.21800000000002</v>
       </c>
       <c r="R59" s="1">
+        <f t="shared" si="14"/>
+        <v>47</v>
+      </c>
+      <c r="S59" s="5">
+        <f t="shared" si="19"/>
+        <v>71.881999999999977</v>
+      </c>
+      <c r="T59" s="1">
+        <f t="shared" si="15"/>
+        <v>11.5</v>
+      </c>
+      <c r="U59" s="1">
         <f t="shared" si="16"/>
-        <v>47</v>
-      </c>
-      <c r="S59" s="5">
-        <f t="shared" si="21"/>
-        <v>71.881999999999977</v>
-      </c>
-      <c r="T59" s="1">
-        <f t="shared" si="17"/>
-        <v>11.5</v>
-      </c>
-      <c r="U59" s="1">
-        <f t="shared" si="18"/>
         <v>9.9705957446808515</v>
       </c>
       <c r="V59" s="1">
@@ -7096,8 +7132,8 @@
       </c>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1">
-        <f t="shared" si="14"/>
-        <v>28.752799999999993</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
@@ -7112,10 +7148,10 @@
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" s="1">
         <v>614.85900000000004</v>
@@ -7136,14 +7172,14 @@
         <v>40</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1">
         <v>491.2</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-30.33299999999997</v>
       </c>
       <c r="M60" s="1"/>
@@ -7156,19 +7192,19 @@
         <v>179.75691999999989</v>
       </c>
       <c r="R60" s="1">
+        <f t="shared" si="14"/>
+        <v>92.173400000000001</v>
+      </c>
+      <c r="S60" s="5">
+        <f t="shared" si="12"/>
+        <v>169.20828</v>
+      </c>
+      <c r="T60" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U60" s="1">
         <f t="shared" si="16"/>
-        <v>92.173400000000001</v>
-      </c>
-      <c r="S60" s="5">
-        <f t="shared" si="13"/>
-        <v>169.20828</v>
-      </c>
-      <c r="T60" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U60" s="1">
-        <f t="shared" si="18"/>
         <v>10.164239574541027</v>
       </c>
       <c r="V60" s="1">
@@ -7203,8 +7239,8 @@
       </c>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1">
-        <f t="shared" si="14"/>
-        <v>169.20828</v>
+        <f t="shared" si="7"/>
+        <v>169</v>
       </c>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
@@ -7219,10 +7255,10 @@
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C61" s="1">
         <v>-1.4930000000000001</v>
@@ -7243,14 +7279,14 @@
         <v>40</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1">
         <v>335</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-32.298999999999978</v>
       </c>
       <c r="M61" s="1"/>
@@ -7263,19 +7299,19 @@
         <v>0</v>
       </c>
       <c r="R61" s="1">
+        <f t="shared" si="14"/>
+        <v>60.540200000000006</v>
+      </c>
+      <c r="S61" s="5">
+        <f t="shared" si="12"/>
+        <v>321.89522650000049</v>
+      </c>
+      <c r="T61" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U61" s="1">
         <f t="shared" si="16"/>
-        <v>60.540200000000006</v>
-      </c>
-      <c r="S61" s="5">
-        <f t="shared" si="13"/>
-        <v>321.89522650000049</v>
-      </c>
-      <c r="T61" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U61" s="1">
-        <f t="shared" si="18"/>
         <v>6.682950725303181</v>
       </c>
       <c r="V61" s="1">
@@ -7309,11 +7345,11 @@
         <v>23.633800000000001</v>
       </c>
       <c r="AF61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="14"/>
-        <v>321.89522650000049</v>
+        <f t="shared" si="7"/>
+        <v>322</v>
       </c>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
@@ -7328,10 +7364,10 @@
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="1">
         <v>1558</v>
@@ -7352,14 +7388,14 @@
         <v>40</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1">
         <v>935</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-13</v>
       </c>
       <c r="M62" s="1"/>
@@ -7372,19 +7408,19 @@
         <v>240.45</v>
       </c>
       <c r="R62" s="1">
+        <f t="shared" si="14"/>
+        <v>184.4</v>
+      </c>
+      <c r="S62" s="5">
+        <f t="shared" si="12"/>
+        <v>686.65000000000032</v>
+      </c>
+      <c r="T62" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U62" s="1">
         <f t="shared" si="16"/>
-        <v>184.4</v>
-      </c>
-      <c r="S62" s="5">
-        <f t="shared" si="13"/>
-        <v>686.65000000000032</v>
-      </c>
-      <c r="T62" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U62" s="1">
-        <f t="shared" si="18"/>
         <v>8.2763015184381761</v>
       </c>
       <c r="V62" s="1">
@@ -7419,8 +7455,8 @@
       </c>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1">
-        <f t="shared" si="14"/>
-        <v>274.66000000000014</v>
+        <f t="shared" si="7"/>
+        <v>275</v>
       </c>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
@@ -7435,10 +7471,10 @@
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="1">
         <v>1100</v>
@@ -7459,14 +7495,14 @@
         <v>40</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1">
         <v>646</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-9</v>
       </c>
       <c r="M63" s="1"/>
@@ -7479,7 +7515,7 @@
         <v>477.30999999999977</v>
       </c>
       <c r="R63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>127.4</v>
       </c>
       <c r="S63" s="5">
@@ -7487,11 +7523,11 @@
         <v>385.09000000000037</v>
       </c>
       <c r="T63" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>11.5</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>8.4773155416012536</v>
       </c>
       <c r="V63" s="1">
@@ -7526,8 +7562,8 @@
       </c>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1">
-        <f t="shared" si="14"/>
-        <v>154.03600000000017</v>
+        <f t="shared" si="7"/>
+        <v>154</v>
       </c>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
@@ -7542,10 +7578,10 @@
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="1">
         <v>180.06800000000001</v>
@@ -7566,14 +7602,14 @@
         <v>40</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1">
         <v>483.17500000000001</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1.0869999999999891</v>
       </c>
       <c r="M64" s="1"/>
@@ -7586,18 +7622,18 @@
         <v>350</v>
       </c>
       <c r="R64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>96.852400000000003</v>
       </c>
       <c r="S64" s="5">
         <v>550</v>
       </c>
       <c r="T64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>9.3088245619107006</v>
       </c>
       <c r="U64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>3.6300804110171763</v>
       </c>
       <c r="V64" s="1">
@@ -7632,7 +7668,7 @@
       </c>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>550</v>
       </c>
       <c r="AH64" s="1"/>
@@ -7648,10 +7684,10 @@
     </row>
     <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" s="1">
         <v>11.618</v>
@@ -7670,14 +7706,14 @@
         <v>40</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1">
         <v>50.575000000000003</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-38.791000000000004</v>
       </c>
       <c r="M65" s="1"/>
@@ -7690,16 +7726,16 @@
         <v>23.038199999999989</v>
       </c>
       <c r="R65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>2.3568000000000002</v>
       </c>
       <c r="S65" s="5"/>
       <c r="T65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>94.636031907671409</v>
       </c>
       <c r="U65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>94.636031907671409</v>
       </c>
       <c r="V65" s="1">
@@ -7734,7 +7770,7 @@
       </c>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH65" s="1"/>
@@ -7750,10 +7786,10 @@
     </row>
     <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" s="1">
         <v>-1.042</v>
@@ -7772,14 +7808,14 @@
         <v>40</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1">
         <v>160.6</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-161.506</v>
       </c>
       <c r="M66" s="1"/>
@@ -7792,18 +7828,18 @@
         <v>105</v>
       </c>
       <c r="R66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-0.1812</v>
       </c>
       <c r="S66" s="5">
         <v>100</v>
       </c>
       <c r="T66" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-1131.346578366446</v>
       </c>
       <c r="U66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>-579.4701986754967</v>
       </c>
       <c r="V66" s="1">
@@ -7838,7 +7874,7 @@
       </c>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1">
-        <f t="shared" ref="AG66:AG84" si="22">G66*S66</f>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="AH66" s="1"/>
@@ -7854,10 +7890,10 @@
     </row>
     <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C67" s="1">
         <v>-10.111000000000001</v>
@@ -7878,14 +7914,14 @@
         <v>40</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1">
         <v>5.6</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-6.5119999999999996</v>
       </c>
       <c r="M67" s="1"/>
@@ -7898,18 +7934,18 @@
         <v>50</v>
       </c>
       <c r="R67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-0.18240000000000001</v>
       </c>
       <c r="S67" s="5">
         <v>30</v>
       </c>
       <c r="T67" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-737.43969298245622</v>
       </c>
       <c r="U67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>-572.96600877192975</v>
       </c>
       <c r="V67" s="1">
@@ -7944,7 +7980,7 @@
       </c>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="AH67" s="1"/>
@@ -7960,10 +7996,10 @@
     </row>
     <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C68" s="1">
         <v>14</v>
@@ -7984,14 +8020,14 @@
         <v>70</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1">
         <v>7</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M68" s="1"/>
@@ -8004,16 +8040,16 @@
         <v>0</v>
       </c>
       <c r="R68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.4</v>
       </c>
       <c r="S68" s="5"/>
       <c r="T68" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>10.714285714285715</v>
       </c>
       <c r="U68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>10.714285714285715</v>
       </c>
       <c r="V68" s="1">
@@ -8048,7 +8084,7 @@
       </c>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH68" s="1"/>
@@ -8064,10 +8100,10 @@
     </row>
     <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C69" s="1">
         <v>208.71</v>
@@ -8088,14 +8124,14 @@
         <v>30</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1">
         <v>198</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-24.27000000000001</v>
       </c>
       <c r="M69" s="1"/>
@@ -8108,19 +8144,19 @@
         <v>70</v>
       </c>
       <c r="R69" s="1">
+        <f t="shared" si="14"/>
+        <v>34.745999999999995</v>
+      </c>
+      <c r="S69" s="5">
+        <f t="shared" si="12"/>
+        <v>85.86179999999996</v>
+      </c>
+      <c r="T69" s="1">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="U69" s="1">
         <f t="shared" si="16"/>
-        <v>34.745999999999995</v>
-      </c>
-      <c r="S69" s="5">
-        <f t="shared" si="13"/>
-        <v>85.86179999999996</v>
-      </c>
-      <c r="T69" s="1">
-        <f t="shared" si="17"/>
-        <v>12</v>
-      </c>
-      <c r="U69" s="1">
-        <f t="shared" si="18"/>
         <v>9.5288723881885691</v>
       </c>
       <c r="V69" s="1">
@@ -8155,8 +8191,8 @@
       </c>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1">
-        <f t="shared" si="22"/>
-        <v>85.86179999999996</v>
+        <f t="shared" si="7"/>
+        <v>86</v>
       </c>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
@@ -8171,10 +8207,10 @@
     </row>
     <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C70" s="1">
         <v>93</v>
@@ -8195,14 +8231,14 @@
         <v>60</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1">
         <v>136</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="23">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
         <v>-5</v>
       </c>
       <c r="M70" s="1"/>
@@ -8215,7 +8251,7 @@
         <v>103.05800000000001</v>
       </c>
       <c r="R70" s="1">
-        <f t="shared" ref="R70:R101" si="24">E70/5</f>
+        <f t="shared" ref="R70:R101" si="21">E70/5</f>
         <v>26.2</v>
       </c>
       <c r="S70" s="5">
@@ -8223,11 +8259,11 @@
         <v>13.442000000000007</v>
       </c>
       <c r="T70" s="1">
-        <f t="shared" ref="T70:T101" si="25">(F70+O70+P70+Q70+S70)/R70</f>
+        <f t="shared" ref="T70:T101" si="22">(F70+O70+P70+Q70+S70)/R70</f>
         <v>11.5</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U101" si="26">(F70+O70+P70+Q70)/R70</f>
+        <f t="shared" ref="U70:U101" si="23">(F70+O70+P70+Q70)/R70</f>
         <v>10.986946564885496</v>
       </c>
       <c r="V70" s="1">
@@ -8262,8 +8298,8 @@
       </c>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1">
-        <f t="shared" si="22"/>
-        <v>8.0652000000000044</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
@@ -8278,10 +8314,10 @@
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C71" s="1">
         <v>8</v>
@@ -8302,14 +8338,14 @@
         <v>60</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1">
         <v>43</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-8</v>
       </c>
       <c r="M71" s="1"/>
@@ -8322,16 +8358,16 @@
         <v>0</v>
       </c>
       <c r="R71" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="S71" s="5"/>
       <c r="T71" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>17.100000000000001</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>17.100000000000001</v>
       </c>
       <c r="V71" s="1">
@@ -8366,7 +8402,7 @@
       </c>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="AG71:AG129" si="24">ROUND(G71*S71,0)</f>
         <v>0</v>
       </c>
       <c r="AH71" s="1"/>
@@ -8382,10 +8418,10 @@
     </row>
     <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C72" s="1">
         <v>144</v>
@@ -8406,14 +8442,14 @@
         <v>90</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1">
         <v>102</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M72" s="1"/>
@@ -8426,16 +8462,16 @@
         <v>15.69999999999999</v>
       </c>
       <c r="R72" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>19.399999999999999</v>
       </c>
       <c r="S72" s="5"/>
       <c r="T72" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>13.525773195876289</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>13.525773195876289</v>
       </c>
       <c r="V72" s="1">
@@ -8470,7 +8506,7 @@
       </c>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH72" s="1"/>
@@ -8486,10 +8522,10 @@
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="1">
         <v>249</v>
@@ -8510,14 +8546,14 @@
         <v>60</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1">
         <v>158</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M73" s="1"/>
@@ -8530,19 +8566,19 @@
         <v>0</v>
       </c>
       <c r="R73" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>30.6</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>43.200000000000045</v>
       </c>
       <c r="T73" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>12.000000000000002</v>
       </c>
       <c r="U73" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.588235294117647</v>
       </c>
       <c r="V73" s="1">
@@ -8577,8 +8613,8 @@
       </c>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1">
-        <f t="shared" si="22"/>
-        <v>14.256000000000016</v>
+        <f t="shared" si="24"/>
+        <v>14</v>
       </c>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
@@ -8593,10 +8629,10 @@
     </row>
     <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C74" s="1">
         <v>82</v>
@@ -8617,14 +8653,14 @@
         <v>90</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1">
         <v>90</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M74" s="1"/>
@@ -8637,16 +8673,16 @@
         <v>30</v>
       </c>
       <c r="R74" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="S74" s="5"/>
       <c r="T74" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>12.058823529411764</v>
       </c>
       <c r="U74" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>12.058823529411764</v>
       </c>
       <c r="V74" s="1">
@@ -8681,7 +8717,7 @@
       </c>
       <c r="AF74" s="1"/>
       <c r="AG74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH74" s="1"/>
@@ -8697,10 +8733,10 @@
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C75" s="1">
         <v>817</v>
@@ -8721,14 +8757,14 @@
         <v>50</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1">
         <v>451</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-23</v>
       </c>
       <c r="M75" s="1"/>
@@ -8741,19 +8777,19 @@
         <v>40.759999999999764</v>
       </c>
       <c r="R75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>85.6</v>
       </c>
       <c r="S75" s="5">
-        <f t="shared" ref="S75:S76" si="27">11.5*R75-Q75-P75-O75-F75</f>
+        <f t="shared" ref="S75:S76" si="25">11.5*R75-Q75-P75-O75-F75</f>
         <v>199.98062800000014</v>
       </c>
       <c r="T75" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U75" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>9.1637777102803728</v>
       </c>
       <c r="V75" s="1">
@@ -8788,8 +8824,8 @@
       </c>
       <c r="AF75" s="1"/>
       <c r="AG75" s="1">
-        <f t="shared" si="22"/>
-        <v>73.992832360000051</v>
+        <f t="shared" si="24"/>
+        <v>74</v>
       </c>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
@@ -8804,10 +8840,10 @@
     </row>
     <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="1">
         <v>386</v>
@@ -8828,14 +8864,14 @@
         <v>70</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1">
         <v>185</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-4</v>
       </c>
       <c r="M76" s="1"/>
@@ -8848,19 +8884,19 @@
         <v>121.15</v>
       </c>
       <c r="R76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>36.200000000000003</v>
       </c>
       <c r="S76" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>61.699999999999932</v>
       </c>
       <c r="T76" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.499999999999998</v>
       </c>
       <c r="U76" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>9.7955801104972373</v>
       </c>
       <c r="V76" s="1">
@@ -8895,8 +8931,8 @@
       </c>
       <c r="AF76" s="1"/>
       <c r="AG76" s="1">
-        <f t="shared" si="22"/>
-        <v>37.01999999999996</v>
+        <f t="shared" si="24"/>
+        <v>37</v>
       </c>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
@@ -8911,10 +8947,10 @@
     </row>
     <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C77" s="1">
         <v>18</v>
@@ -8935,14 +8971,14 @@
         <v>40</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1">
         <v>32</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="M77" s="1"/>
@@ -8955,16 +8991,16 @@
         <v>0</v>
       </c>
       <c r="R77" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="S77" s="5"/>
       <c r="T77" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>21.386363636363633</v>
       </c>
       <c r="U77" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>21.386363636363633</v>
       </c>
       <c r="V77" s="1">
@@ -8999,7 +9035,7 @@
       </c>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH77" s="1"/>
@@ -9015,10 +9051,10 @@
     </row>
     <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="1">
         <v>420</v>
@@ -9039,14 +9075,14 @@
         <v>55</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1">
         <v>227</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M78" s="1"/>
@@ -9059,7 +9095,7 @@
         <v>103.1</v>
       </c>
       <c r="R78" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>44.4</v>
       </c>
       <c r="S78" s="5">
@@ -9067,11 +9103,11 @@
         <v>35.417867999999999</v>
       </c>
       <c r="T78" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U78" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.702300270270271</v>
       </c>
       <c r="V78" s="1">
@@ -9106,8 +9142,8 @@
       </c>
       <c r="AF78" s="1"/>
       <c r="AG78" s="1">
-        <f t="shared" si="22"/>
-        <v>14.1671472</v>
+        <f t="shared" si="24"/>
+        <v>14</v>
       </c>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
@@ -9122,10 +9158,10 @@
     </row>
     <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
@@ -9142,14 +9178,14 @@
         <v>40</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1">
         <v>3</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-4</v>
       </c>
       <c r="M79" s="1"/>
@@ -9162,18 +9198,18 @@
         <v>10</v>
       </c>
       <c r="R79" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>-0.2</v>
       </c>
       <c r="S79" s="5">
         <v>10</v>
       </c>
       <c r="T79" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-250</v>
       </c>
       <c r="U79" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>-200</v>
       </c>
       <c r="V79" s="1">
@@ -9208,8 +9244,8 @@
       </c>
       <c r="AF79" s="1"/>
       <c r="AG79" s="1">
-        <f t="shared" si="22"/>
-        <v>3.5</v>
+        <f t="shared" si="24"/>
+        <v>4</v>
       </c>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
@@ -9224,10 +9260,10 @@
     </row>
     <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C80" s="1">
         <v>123</v>
@@ -9246,14 +9282,14 @@
         <v>45</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1">
         <v>149</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-26</v>
       </c>
       <c r="M80" s="1"/>
@@ -9266,18 +9302,18 @@
         <v>105</v>
       </c>
       <c r="R80" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>24.6</v>
       </c>
       <c r="S80" s="5">
         <v>20</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>13.560975609756097</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>12.747967479674797</v>
       </c>
       <c r="V80" s="1">
@@ -9312,7 +9348,7 @@
       </c>
       <c r="AF80" s="1"/>
       <c r="AG80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="AH80" s="1"/>
@@ -9328,10 +9364,10 @@
     </row>
     <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C81" s="1">
         <v>183</v>
@@ -9352,14 +9388,14 @@
         <v>55</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1">
         <v>190</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
       <c r="M81" s="1"/>
@@ -9372,7 +9408,7 @@
         <v>198.06</v>
       </c>
       <c r="R81" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>35.799999999999997</v>
       </c>
       <c r="S81" s="5">
@@ -9380,11 +9416,11 @@
         <v>45.039999999999964</v>
       </c>
       <c r="T81" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U81" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.241899441340784</v>
       </c>
       <c r="V81" s="1">
@@ -9419,8 +9455,8 @@
       </c>
       <c r="AF81" s="1"/>
       <c r="AG81" s="1">
-        <f t="shared" si="22"/>
-        <v>18.015999999999988</v>
+        <f t="shared" si="24"/>
+        <v>18</v>
       </c>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
@@ -9435,10 +9471,10 @@
     </row>
     <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
         <v>20.181000000000001</v>
@@ -9459,14 +9495,14 @@
         <v>55</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1">
         <v>5.3</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0.42300000000000004</v>
       </c>
       <c r="M82" s="1"/>
@@ -9479,16 +9515,16 @@
         <v>0</v>
       </c>
       <c r="R82" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>1.1446000000000001</v>
       </c>
       <c r="S82" s="5"/>
       <c r="T82" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>58.187139612091556</v>
       </c>
       <c r="U82" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>58.187139612091556</v>
       </c>
       <c r="V82" s="1">
@@ -9522,10 +9558,10 @@
         <v>4.3439999999999994</v>
       </c>
       <c r="AF82" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH82" s="1"/>
@@ -9541,10 +9577,10 @@
     </row>
     <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C83" s="1">
         <v>220.09700000000001</v>
@@ -9565,14 +9601,14 @@
         <v>55</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1">
         <v>118.3</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>8.7729999999999961</v>
       </c>
       <c r="M83" s="1"/>
@@ -9585,19 +9621,19 @@
         <v>17.22039999999998</v>
       </c>
       <c r="R83" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>25.4146</v>
       </c>
       <c r="S83" s="5">
-        <f t="shared" ref="S83:S84" si="28">11.5*R83-Q83-P83-O83-F83</f>
+        <f t="shared" ref="S83:S84" si="26">11.5*R83-Q83-P83-O83-F83</f>
         <v>126.80850000000001</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U83" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>6.5104074036183919</v>
       </c>
       <c r="V83" s="1">
@@ -9632,8 +9668,8 @@
       </c>
       <c r="AF83" s="1"/>
       <c r="AG83" s="1">
-        <f t="shared" si="22"/>
-        <v>126.80850000000001</v>
+        <f t="shared" si="24"/>
+        <v>127</v>
       </c>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
@@ -9648,10 +9684,10 @@
     </row>
     <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>1085.3789999999999</v>
@@ -9672,14 +9708,14 @@
         <v>60</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1">
         <v>648.19500000000005</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5.1009999999999991</v>
       </c>
       <c r="M84" s="1"/>
@@ -9692,19 +9728,19 @@
         <v>111.78016388319971</v>
       </c>
       <c r="R84" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>128.61880000000002</v>
       </c>
       <c r="S84" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>184.4218586537587</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.499999999999998</v>
       </c>
       <c r="U84" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.066136065227177</v>
       </c>
       <c r="V84" s="1">
@@ -9739,8 +9775,8 @@
       </c>
       <c r="AF84" s="1"/>
       <c r="AG84" s="1">
-        <f t="shared" si="22"/>
-        <v>184.4218586537587</v>
+        <f t="shared" si="24"/>
+        <v>184</v>
       </c>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
@@ -9755,10 +9791,10 @@
     </row>
     <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -9769,12 +9805,12 @@
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -9787,16 +9823,16 @@
         <v>0</v>
       </c>
       <c r="R85" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S85" s="12"/>
       <c r="T85" s="10" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" s="10">
@@ -9830,9 +9866,12 @@
         <v>0</v>
       </c>
       <c r="AF85" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG85" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG85" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
@@ -9846,10 +9885,10 @@
     </row>
     <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
         <v>4689.6670000000004</v>
@@ -9870,14 +9909,14 @@
         <v>60</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1">
         <v>2145.5</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-5.9859999999998763</v>
       </c>
       <c r="M86" s="1"/>
@@ -9892,19 +9931,19 @@
         <v>320.75844000000029</v>
       </c>
       <c r="R86" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>427.90280000000001</v>
       </c>
       <c r="S86" s="5">
-        <f t="shared" ref="S86:S88" si="29">11.5*R86-Q86-P86-O86-F86</f>
+        <f t="shared" ref="S86:S88" si="27">11.5*R86-Q86-P86-O86-F86</f>
         <v>369.2827599999996</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U86" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.636993821961438</v>
       </c>
       <c r="V86" s="1">
@@ -9939,8 +9978,8 @@
       </c>
       <c r="AF86" s="1"/>
       <c r="AG86" s="1">
-        <f t="shared" ref="AG86:AG91" si="30">G86*S86</f>
-        <v>369.2827599999996</v>
+        <f t="shared" si="24"/>
+        <v>369</v>
       </c>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
@@ -9955,10 +9994,10 @@
     </row>
     <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C87" s="1">
         <v>4872.7489999999998</v>
@@ -9979,14 +10018,14 @@
         <v>60</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1">
         <v>2144.1</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>30.963999999999942</v>
       </c>
       <c r="M87" s="1"/>
@@ -9999,19 +10038,19 @@
         <v>77.056429999999978</v>
       </c>
       <c r="R87" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>435.01279999999997</v>
       </c>
       <c r="S87" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1179.1177699999998</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U87" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>8.78946419507656</v>
       </c>
       <c r="V87" s="1">
@@ -10046,8 +10085,8 @@
       </c>
       <c r="AF87" s="1"/>
       <c r="AG87" s="1">
-        <f t="shared" si="30"/>
-        <v>1179.1177699999998</v>
+        <f t="shared" si="24"/>
+        <v>1179</v>
       </c>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
@@ -10062,10 +10101,10 @@
     </row>
     <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C88" s="1">
         <v>4617.2650000000003</v>
@@ -10086,14 +10125,14 @@
         <v>60</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1">
         <v>2351.6</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-32.877999999999702</v>
       </c>
       <c r="M88" s="1"/>
@@ -10106,19 +10145,19 @@
         <v>110.40345514700221</v>
       </c>
       <c r="R88" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>463.74440000000004</v>
       </c>
       <c r="S88" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>385.28814485299881</v>
       </c>
       <c r="T88" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U88" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>10.669179951600498</v>
       </c>
       <c r="V88" s="1">
@@ -10153,8 +10192,8 @@
       </c>
       <c r="AF88" s="1"/>
       <c r="AG88" s="1">
-        <f t="shared" si="30"/>
-        <v>385.28814485299881</v>
+        <f t="shared" si="24"/>
+        <v>385</v>
       </c>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
@@ -10169,10 +10208,10 @@
     </row>
     <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
         <v>51.786000000000001</v>
@@ -10193,14 +10232,14 @@
         <v>55</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1">
         <v>34.6</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>8.6999999999996191E-2</v>
       </c>
       <c r="M89" s="1"/>
@@ -10213,16 +10252,16 @@
         <v>0</v>
       </c>
       <c r="R89" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>6.9373999999999993</v>
       </c>
       <c r="S89" s="5"/>
       <c r="T89" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>18.2732724075302</v>
       </c>
       <c r="U89" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>18.2732724075302</v>
       </c>
       <c r="V89" s="1">
@@ -10257,7 +10296,7 @@
       </c>
       <c r="AF89" s="1"/>
       <c r="AG89" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH89" s="1"/>
@@ -10273,10 +10312,10 @@
     </row>
     <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -10291,12 +10330,12 @@
         <v>40</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M90" s="1"/>
@@ -10309,18 +10348,18 @@
         <v>10</v>
       </c>
       <c r="R90" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>-0.2</v>
       </c>
       <c r="S90" s="5">
         <v>10</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-100</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>-50</v>
       </c>
       <c r="V90" s="1">
@@ -10355,7 +10394,7 @@
       </c>
       <c r="AF90" s="1"/>
       <c r="AG90" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="AH90" s="1"/>
@@ -10371,10 +10410,10 @@
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C91" s="1">
         <v>609</v>
@@ -10395,14 +10434,14 @@
         <v>40</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1">
         <v>104</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-7</v>
       </c>
       <c r="M91" s="1"/>
@@ -10415,16 +10454,16 @@
         <v>0</v>
       </c>
       <c r="R91" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>19.399999999999999</v>
       </c>
       <c r="S91" s="5"/>
       <c r="T91" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>22.783505154639176</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>22.783505154639176</v>
       </c>
       <c r="V91" s="1">
@@ -10458,10 +10497,10 @@
         <v>47.4</v>
       </c>
       <c r="AF91" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG91" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH91" s="1"/>
@@ -10477,10 +10516,10 @@
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
@@ -10491,12 +10530,12 @@
       </c>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
       <c r="L92" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M92" s="10"/>
@@ -10509,16 +10548,16 @@
         <v>0</v>
       </c>
       <c r="R92" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S92" s="12"/>
       <c r="T92" s="10" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" s="10">
@@ -10552,9 +10591,12 @@
         <v>0</v>
       </c>
       <c r="AF92" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG92" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG92" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
@@ -10568,10 +10610,10 @@
     </row>
     <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C93" s="1">
         <v>169</v>
@@ -10592,14 +10634,14 @@
         <v>90</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1">
         <v>151</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-4</v>
       </c>
       <c r="M93" s="1"/>
@@ -10612,19 +10654,19 @@
         <v>126</v>
       </c>
       <c r="R93" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>29.4</v>
       </c>
       <c r="S93" s="5">
-        <f t="shared" ref="S93:S96" si="31">12*R93-Q93-P93-O93-F93</f>
+        <f t="shared" ref="S93:S96" si="28">12*R93-Q93-P93-O93-F93</f>
         <v>158.1</v>
       </c>
       <c r="T93" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.999999999999998</v>
       </c>
       <c r="U93" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>6.6224489795918355</v>
       </c>
       <c r="V93" s="1">
@@ -10659,8 +10701,8 @@
       </c>
       <c r="AF93" s="1"/>
       <c r="AG93" s="1">
-        <f>G93*S93</f>
-        <v>11.067</v>
+        <f t="shared" si="24"/>
+        <v>11</v>
       </c>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
@@ -10675,10 +10717,10 @@
     </row>
     <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C94" s="1">
         <v>196</v>
@@ -10699,14 +10741,14 @@
         <v>90</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1">
         <v>131</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="M94" s="1"/>
@@ -10719,19 +10761,19 @@
         <v>65.449999999999974</v>
       </c>
       <c r="R94" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>24.2</v>
       </c>
       <c r="S94" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>83.44999999999996</v>
       </c>
       <c r="T94" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>8.5516528925619841</v>
       </c>
       <c r="V94" s="1">
@@ -10766,8 +10808,8 @@
       </c>
       <c r="AF94" s="1"/>
       <c r="AG94" s="1">
-        <f>G94*S94</f>
-        <v>5.8414999999999981</v>
+        <f t="shared" si="24"/>
+        <v>6</v>
       </c>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
@@ -10782,10 +10824,10 @@
     </row>
     <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C95" s="1">
         <v>106</v>
@@ -10806,14 +10848,14 @@
         <v>40</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1">
         <v>130</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-29</v>
       </c>
       <c r="M95" s="1"/>
@@ -10826,16 +10868,16 @@
         <v>0</v>
       </c>
       <c r="R95" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>20.2</v>
       </c>
       <c r="S95" s="5"/>
       <c r="T95" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>15.64851485148515</v>
       </c>
       <c r="U95" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>15.64851485148515</v>
       </c>
       <c r="V95" s="1">
@@ -10870,7 +10912,7 @@
       </c>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1">
-        <f>G95*S95</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH95" s="1"/>
@@ -10886,10 +10928,10 @@
     </row>
     <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C96" s="1">
         <v>134.93299999999999</v>
@@ -10911,14 +10953,14 @@
         <v>55</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1">
         <v>88.6</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-2.7199999999999989</v>
       </c>
       <c r="M96" s="1"/>
@@ -10931,19 +10973,19 @@
         <v>54.961759999999977</v>
       </c>
       <c r="R96" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>17.175999999999998</v>
       </c>
       <c r="S96" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>48.156439999999989</v>
       </c>
       <c r="T96" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="U96" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>9.1962948299953435</v>
       </c>
       <c r="V96" s="1">
@@ -10978,8 +11020,8 @@
       </c>
       <c r="AF96" s="1"/>
       <c r="AG96" s="1">
-        <f>G96*S96</f>
-        <v>48.156439999999989</v>
+        <f t="shared" si="24"/>
+        <v>48</v>
       </c>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
@@ -10994,10 +11036,10 @@
     </row>
     <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
@@ -11008,12 +11050,12 @@
       </c>
       <c r="H97" s="10"/>
       <c r="I97" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
       <c r="L97" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M97" s="10"/>
@@ -11026,16 +11068,16 @@
         <v>0</v>
       </c>
       <c r="R97" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S97" s="12"/>
       <c r="T97" s="10" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" s="10">
@@ -11069,9 +11111,12 @@
         <v>0</v>
       </c>
       <c r="AF97" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG97" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG97" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
@@ -11085,10 +11130,10 @@
     </row>
     <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -11101,12 +11146,12 @@
         <v>30</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M98" s="1"/>
@@ -11119,18 +11164,18 @@
         <v>0</v>
       </c>
       <c r="R98" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S98" s="5">
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="S98" s="18">
+        <v>0</v>
       </c>
       <c r="T98" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U98" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V98" s="1">
@@ -11163,12 +11208,12 @@
       <c r="AE98" s="1">
         <v>-0.2</v>
       </c>
-      <c r="AF98" s="1" t="s">
-        <v>137</v>
+      <c r="AF98" s="19" t="s">
+        <v>177</v>
       </c>
       <c r="AG98" s="1">
-        <f t="shared" ref="AG98:AG104" si="32">G98*S98</f>
-        <v>2</v>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
@@ -11183,10 +11228,10 @@
     </row>
     <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C99" s="1">
         <v>378</v>
@@ -11207,14 +11252,14 @@
         <v>45</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
         <v>230</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
       <c r="M99" s="1"/>
@@ -11227,19 +11272,19 @@
         <v>96.213999999999999</v>
       </c>
       <c r="R99" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>43.8</v>
       </c>
       <c r="S99" s="5">
-        <f t="shared" ref="S99:S100" si="33">11.5*R99-Q99-P99-O99-F99</f>
+        <f t="shared" ref="S99:S100" si="29">11.5*R99-Q99-P99-O99-F99</f>
         <v>74.685999999999979</v>
       </c>
       <c r="T99" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U99" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>9.7948401826484019</v>
       </c>
       <c r="V99" s="1">
@@ -11274,8 +11319,8 @@
       </c>
       <c r="AF99" s="1"/>
       <c r="AG99" s="1">
-        <f t="shared" si="32"/>
-        <v>5.9748799999999989</v>
+        <f t="shared" si="24"/>
+        <v>6</v>
       </c>
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
@@ -11290,10 +11335,10 @@
     </row>
     <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C100" s="1">
         <v>272</v>
@@ -11314,14 +11359,14 @@
         <v>45</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1">
         <v>218</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-13</v>
       </c>
       <c r="M100" s="1"/>
@@ -11334,19 +11379,19 @@
         <v>107.718</v>
       </c>
       <c r="R100" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>41</v>
       </c>
       <c r="S100" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="29"/>
         <v>111.98199999999997</v>
       </c>
       <c r="T100" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>11.5</v>
       </c>
       <c r="U100" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>8.7687317073170732</v>
       </c>
       <c r="V100" s="1">
@@ -11381,8 +11426,8 @@
       </c>
       <c r="AF100" s="1"/>
       <c r="AG100" s="1">
-        <f t="shared" si="32"/>
-        <v>8.9585599999999985</v>
+        <f t="shared" si="24"/>
+        <v>9</v>
       </c>
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
@@ -11397,10 +11442,10 @@
     </row>
     <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C101" s="1">
         <v>4</v>
@@ -11421,14 +11466,14 @@
         <v>30</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1">
         <v>8</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-11</v>
       </c>
       <c r="M101" s="1"/>
@@ -11441,16 +11486,16 @@
         <v>0</v>
       </c>
       <c r="R101" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>-0.6</v>
       </c>
       <c r="S101" s="5"/>
       <c r="T101" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-71.666666666666671</v>
       </c>
       <c r="U101" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>-71.666666666666671</v>
       </c>
       <c r="V101" s="1">
@@ -11484,10 +11529,10 @@
         <v>0</v>
       </c>
       <c r="AF101" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG101" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH101" s="1"/>
@@ -11503,10 +11548,10 @@
     </row>
     <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C102" s="1">
         <v>133.19</v>
@@ -11527,14 +11572,14 @@
         <v>40</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J102" s="1"/>
       <c r="K102" s="1">
         <v>354.7</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="34">E102-K102</f>
+        <f t="shared" ref="L102:L129" si="30">E102-K102</f>
         <v>-222</v>
       </c>
       <c r="M102" s="1"/>
@@ -11547,18 +11592,18 @@
         <v>45.806999999999938</v>
       </c>
       <c r="R102" s="1">
-        <f t="shared" ref="R102:R129" si="35">E102/5</f>
+        <f t="shared" ref="R102:R129" si="31">E102/5</f>
         <v>26.54</v>
       </c>
       <c r="S102" s="5">
         <v>50</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" ref="T102:T133" si="36">(F102+O102+P102+Q102+S102)/R102</f>
+        <f t="shared" ref="T102:T129" si="32">(F102+O102+P102+Q102+S102)/R102</f>
         <v>29.471590052750564</v>
       </c>
       <c r="U102" s="1">
-        <f t="shared" ref="U102:U129" si="37">(F102+O102+P102+Q102)/R102</f>
+        <f t="shared" ref="U102:U129" si="33">(F102+O102+P102+Q102)/R102</f>
         <v>27.587641296156743</v>
       </c>
       <c r="V102" s="1">
@@ -11592,10 +11637,10 @@
         <v>43.054199999999987</v>
       </c>
       <c r="AF102" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG102" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>50</v>
       </c>
       <c r="AH102" s="1"/>
@@ -11611,10 +11656,10 @@
     </row>
     <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C103" s="1">
         <v>452.38900000000001</v>
@@ -11635,14 +11680,14 @@
         <v>40</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1">
         <v>992.2</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-96.807000000000016</v>
       </c>
       <c r="M103" s="1"/>
@@ -11655,18 +11700,18 @@
         <v>700</v>
       </c>
       <c r="R103" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>179.07859999999999</v>
       </c>
       <c r="S103" s="5">
         <v>1000</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>10.994222648602346</v>
       </c>
       <c r="U103" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>5.4100825000865544</v>
       </c>
       <c r="V103" s="1">
@@ -11700,10 +11745,10 @@
         <v>29.4024</v>
       </c>
       <c r="AF103" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG103" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="24"/>
         <v>1000</v>
       </c>
       <c r="AH103" s="1"/>
@@ -11719,10 +11764,10 @@
     </row>
     <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
@@ -11741,14 +11786,14 @@
         <v>40</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1">
         <v>173.7</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-121.73299999999999</v>
       </c>
       <c r="M104" s="1"/>
@@ -11761,19 +11806,19 @@
         <v>0</v>
       </c>
       <c r="R104" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>10.3934</v>
       </c>
       <c r="S104" s="5">
-        <f t="shared" ref="S98:S104" si="38">12*R104-Q104-P104-O104-F104</f>
+        <f t="shared" ref="S104" si="34">12*R104-Q104-P104-O104-F104</f>
         <v>105.93680000000001</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>12</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>1.8073007870379278</v>
       </c>
       <c r="V104" s="1">
@@ -11808,8 +11853,8 @@
       </c>
       <c r="AF104" s="1"/>
       <c r="AG104" s="1">
-        <f t="shared" si="32"/>
-        <v>105.93680000000001</v>
+        <f t="shared" si="24"/>
+        <v>106</v>
       </c>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
@@ -11824,10 +11869,10 @@
     </row>
     <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
@@ -11838,12 +11883,12 @@
       </c>
       <c r="H105" s="10"/>
       <c r="I105" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
       <c r="L105" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M105" s="10"/>
@@ -11856,16 +11901,16 @@
         <v>0</v>
       </c>
       <c r="R105" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S105" s="12"/>
       <c r="T105" s="10" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" s="10">
@@ -11899,9 +11944,12 @@
         <v>0</v>
       </c>
       <c r="AF105" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG105" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG105" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
@@ -11915,10 +11963,10 @@
     </row>
     <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>41.156999999999996</v>
@@ -11939,14 +11987,14 @@
         <v>55</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1">
         <v>19.100000000000001</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>5.6499999999999986</v>
       </c>
       <c r="M106" s="1"/>
@@ -11959,7 +12007,7 @@
         <v>27.62</v>
       </c>
       <c r="R106" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>4.95</v>
       </c>
       <c r="S106" s="5">
@@ -11967,11 +12015,11 @@
         <v>5.1930000000000049</v>
       </c>
       <c r="T106" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>11.5</v>
       </c>
       <c r="U106" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>10.450909090909091</v>
       </c>
       <c r="V106" s="1">
@@ -12005,11 +12053,11 @@
         <v>2.9998</v>
       </c>
       <c r="AF106" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG106" s="1">
-        <f>G106*S106</f>
-        <v>5.1930000000000049</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
@@ -12024,10 +12072,10 @@
     </row>
     <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C107" s="1">
         <v>74</v>
@@ -12048,14 +12096,14 @@
         <v>40</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1">
         <v>608</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-572</v>
       </c>
       <c r="M107" s="1"/>
@@ -12068,16 +12116,16 @@
         <v>0</v>
       </c>
       <c r="R107" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>7.2</v>
       </c>
       <c r="S107" s="5"/>
       <c r="T107" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>37.916666666666664</v>
       </c>
       <c r="U107" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>37.916666666666664</v>
       </c>
       <c r="V107" s="1">
@@ -12111,10 +12159,10 @@
         <v>9.6</v>
       </c>
       <c r="AF107" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG107" s="1">
-        <f>G107*S107</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH107" s="1"/>
@@ -12130,10 +12178,10 @@
     </row>
     <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
@@ -12144,12 +12192,12 @@
       </c>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J108" s="10"/>
       <c r="K108" s="10"/>
       <c r="L108" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M108" s="10"/>
@@ -12162,16 +12210,16 @@
         <v>0</v>
       </c>
       <c r="R108" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S108" s="12"/>
       <c r="T108" s="10" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" s="10">
@@ -12205,9 +12253,12 @@
         <v>0</v>
       </c>
       <c r="AF108" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG108" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG108" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
@@ -12221,10 +12272,10 @@
     </row>
     <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C109" s="1">
         <v>72</v>
@@ -12245,14 +12296,14 @@
         <v>40</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1">
         <v>581</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-555</v>
       </c>
       <c r="M109" s="1"/>
@@ -12265,16 +12316,16 @@
         <v>0</v>
       </c>
       <c r="R109" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>5.2</v>
       </c>
       <c r="S109" s="5"/>
       <c r="T109" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>47.78846153846154</v>
       </c>
       <c r="U109" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>47.78846153846154</v>
       </c>
       <c r="V109" s="1">
@@ -12308,10 +12359,10 @@
         <v>12</v>
       </c>
       <c r="AF109" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG109" s="1">
-        <f>G109*S109</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH109" s="1"/>
@@ -12327,10 +12378,10 @@
     </row>
     <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C110" s="1">
         <v>135</v>
@@ -12349,14 +12400,14 @@
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J110" s="1"/>
       <c r="K110" s="1">
         <v>117</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-12</v>
       </c>
       <c r="M110" s="1"/>
@@ -12369,7 +12420,7 @@
         <v>22.148000000000049</v>
       </c>
       <c r="R110" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>21</v>
       </c>
       <c r="S110" s="5">
@@ -12377,11 +12428,11 @@
         <v>43.551999999999992</v>
       </c>
       <c r="T110" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>11.5</v>
       </c>
       <c r="U110" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>9.4260952380952379</v>
       </c>
       <c r="V110" s="1">
@@ -12416,8 +12467,8 @@
       </c>
       <c r="AF110" s="1"/>
       <c r="AG110" s="1">
-        <f>G110*S110</f>
-        <v>3.9196799999999992</v>
+        <f t="shared" si="24"/>
+        <v>4</v>
       </c>
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
@@ -12432,10 +12483,10 @@
     </row>
     <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C111" s="1">
         <v>206.69</v>
@@ -12456,14 +12507,14 @@
         <v>60</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1">
         <v>70</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0.87099999999999511</v>
       </c>
       <c r="M111" s="1"/>
@@ -12476,16 +12527,16 @@
         <v>102.4038</v>
       </c>
       <c r="R111" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>14.174199999999999</v>
       </c>
       <c r="S111" s="5"/>
       <c r="T111" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>32.897433364845988</v>
       </c>
       <c r="U111" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>32.897433364845988</v>
       </c>
       <c r="V111" s="1">
@@ -12519,10 +12570,10 @@
         <v>38.171399999999998</v>
       </c>
       <c r="AF111" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG111" s="1">
-        <f>G111*S111</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH111" s="1"/>
@@ -12538,10 +12589,10 @@
     </row>
     <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1">
         <v>89.655000000000001</v>
@@ -12558,14 +12609,14 @@
         <v>50</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1">
         <v>15</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-15</v>
       </c>
       <c r="M112" s="1"/>
@@ -12578,16 +12629,16 @@
         <v>0</v>
       </c>
       <c r="R112" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S112" s="5"/>
       <c r="T112" s="1" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U112" s="1" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V112" s="1">
@@ -12621,10 +12672,10 @@
         <v>0</v>
       </c>
       <c r="AF112" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG112" s="1">
-        <f>G112*S112</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH112" s="1"/>
@@ -12640,10 +12691,10 @@
     </row>
     <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C113" s="1">
         <v>130</v>
@@ -12662,14 +12713,14 @@
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1">
         <v>64</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-5</v>
       </c>
       <c r="M113" s="1"/>
@@ -12682,7 +12733,7 @@
         <v>58.599999999999987</v>
       </c>
       <c r="R113" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>11.8</v>
       </c>
       <c r="S113" s="5">
@@ -12690,11 +12741,11 @@
         <v>11.100000000000023</v>
       </c>
       <c r="T113" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>11.5</v>
       </c>
       <c r="U113" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>10.559322033898304</v>
       </c>
       <c r="V113" s="1">
@@ -12729,8 +12780,8 @@
       </c>
       <c r="AF113" s="1"/>
       <c r="AG113" s="1">
-        <f>G113*S113</f>
-        <v>0.999000000000002</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
@@ -12745,10 +12796,10 @@
     </row>
     <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C114" s="10"/>
       <c r="D114" s="10"/>
@@ -12759,12 +12810,12 @@
       </c>
       <c r="H114" s="10"/>
       <c r="I114" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J114" s="10"/>
       <c r="K114" s="10"/>
       <c r="L114" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M114" s="10"/>
@@ -12777,16 +12828,16 @@
         <v>0</v>
       </c>
       <c r="R114" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S114" s="12"/>
       <c r="T114" s="10" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U114" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V114" s="10">
@@ -12820,9 +12871,12 @@
         <v>0</v>
       </c>
       <c r="AF114" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG114" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="AG114" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
@@ -12836,10 +12890,10 @@
     </row>
     <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C115" s="1">
         <v>802.68100000000004</v>
@@ -12860,14 +12914,14 @@
         <v>60</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J115" s="1"/>
       <c r="K115" s="1">
         <v>338.65</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>10.999000000000024</v>
       </c>
       <c r="M115" s="1"/>
@@ -12880,16 +12934,16 @@
         <v>155.28096199999979</v>
       </c>
       <c r="R115" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>69.9298</v>
       </c>
       <c r="S115" s="5"/>
       <c r="T115" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>11.867012346667657</v>
       </c>
       <c r="U115" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>11.867012346667657</v>
       </c>
       <c r="V115" s="1">
@@ -12924,7 +12978,7 @@
       </c>
       <c r="AF115" s="1"/>
       <c r="AG115" s="1">
-        <f t="shared" ref="AG115:AG121" si="39">G115*S115</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH115" s="1"/>
@@ -12940,10 +12994,10 @@
     </row>
     <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C116" s="1">
         <v>893.08100000000002</v>
@@ -12964,14 +13018,14 @@
         <v>60</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J116" s="1"/>
       <c r="K116" s="1">
         <v>425.75</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>14.663999999999987</v>
       </c>
       <c r="M116" s="1"/>
@@ -12984,16 +13038,16 @@
         <v>13.45441600000049</v>
       </c>
       <c r="R116" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>88.082799999999992</v>
       </c>
       <c r="S116" s="5"/>
       <c r="T116" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>12.023487946727402</v>
       </c>
       <c r="U116" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>12.023487946727402</v>
       </c>
       <c r="V116" s="1">
@@ -13028,7 +13082,7 @@
       </c>
       <c r="AF116" s="1"/>
       <c r="AG116" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH116" s="1"/>
@@ -13044,10 +13098,10 @@
     </row>
     <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C117" s="1">
         <v>414.91199999999998</v>
@@ -13068,14 +13122,14 @@
         <v>60</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J117" s="1"/>
       <c r="K117" s="1">
         <v>129.30000000000001</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-0.14200000000002433</v>
       </c>
       <c r="M117" s="1"/>
@@ -13088,16 +13142,16 @@
         <v>0</v>
       </c>
       <c r="R117" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>25.831599999999998</v>
       </c>
       <c r="S117" s="5"/>
       <c r="T117" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>13.008253457006148</v>
       </c>
       <c r="U117" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>13.008253457006148</v>
       </c>
       <c r="V117" s="1">
@@ -13132,7 +13186,7 @@
       </c>
       <c r="AF117" s="1"/>
       <c r="AG117" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH117" s="1"/>
@@ -13148,10 +13202,10 @@
     </row>
     <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C118" s="1">
         <v>2344.6590000000001</v>
@@ -13172,14 +13226,14 @@
         <v>60</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J118" s="1"/>
       <c r="K118" s="1">
         <v>1584.8</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-34.565000000000055</v>
       </c>
       <c r="M118" s="1"/>
@@ -13192,7 +13246,7 @@
         <v>187.11131594844011</v>
       </c>
       <c r="R118" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>310.04699999999997</v>
       </c>
       <c r="S118" s="5">
@@ -13200,11 +13254,11 @@
         <v>442.43718405155937</v>
       </c>
       <c r="T118" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>11.500000000000002</v>
       </c>
       <c r="U118" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>10.072999628922199</v>
       </c>
       <c r="V118" s="1">
@@ -13239,8 +13293,8 @@
       </c>
       <c r="AF118" s="1"/>
       <c r="AG118" s="1">
-        <f t="shared" si="39"/>
-        <v>442.43718405155937</v>
+        <f t="shared" si="24"/>
+        <v>442</v>
       </c>
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
@@ -13255,10 +13309,10 @@
     </row>
     <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C119" s="1">
         <v>247</v>
@@ -13279,14 +13333,14 @@
         <v>1096</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J119" s="1"/>
       <c r="K119" s="1">
         <v>15</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M119" s="1"/>
@@ -13299,16 +13353,16 @@
         <v>0</v>
       </c>
       <c r="R119" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="S119" s="5"/>
       <c r="T119" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>72.333333333333329</v>
       </c>
       <c r="U119" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>72.333333333333329</v>
       </c>
       <c r="V119" s="1">
@@ -13342,10 +13396,10 @@
         <v>5.8</v>
       </c>
       <c r="AF119" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG119" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH119" s="1"/>
@@ -13361,10 +13415,10 @@
     </row>
     <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C120" s="1">
         <v>338</v>
@@ -13383,14 +13437,14 @@
         <v>1096</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1">
         <v>9</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M120" s="1"/>
@@ -13403,16 +13457,16 @@
         <v>0</v>
       </c>
       <c r="R120" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>1.8</v>
       </c>
       <c r="S120" s="5"/>
       <c r="T120" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>178.88888888888889</v>
       </c>
       <c r="U120" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>178.88888888888889</v>
       </c>
       <c r="V120" s="1">
@@ -13446,10 +13500,10 @@
         <v>5.6</v>
       </c>
       <c r="AF120" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG120" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH120" s="1"/>
@@ -13465,10 +13519,10 @@
     </row>
     <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C121" s="1">
         <v>117</v>
@@ -13489,14 +13543,14 @@
         <v>1096</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J121" s="1"/>
       <c r="K121" s="1">
         <v>20</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M121" s="1"/>
@@ -13509,16 +13563,16 @@
         <v>0</v>
       </c>
       <c r="R121" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>4</v>
       </c>
       <c r="S121" s="5"/>
       <c r="T121" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>32</v>
       </c>
       <c r="U121" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>32</v>
       </c>
       <c r="V121" s="1">
@@ -13552,10 +13606,10 @@
         <v>5.2</v>
       </c>
       <c r="AF121" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG121" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH121" s="1"/>
@@ -13571,10 +13625,10 @@
     </row>
     <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C122" s="10">
         <v>94.091999999999999</v>
@@ -13591,14 +13645,14 @@
       </c>
       <c r="H122" s="10"/>
       <c r="I122" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J122" s="10"/>
       <c r="K122" s="10">
         <v>1.3</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>4.2000000000000037E-2</v>
       </c>
       <c r="M122" s="10"/>
@@ -13611,16 +13665,16 @@
         <v>0</v>
       </c>
       <c r="R122" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0.26840000000000003</v>
       </c>
       <c r="S122" s="12"/>
       <c r="T122" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>342.77198211624437</v>
       </c>
       <c r="U122" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>342.77198211624437</v>
       </c>
       <c r="V122" s="10">
@@ -13654,9 +13708,12 @@
         <v>0</v>
       </c>
       <c r="AF122" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG122" s="10"/>
+        <v>163</v>
+      </c>
+      <c r="AG122" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
       <c r="AJ122" s="1"/>
@@ -13670,10 +13727,10 @@
     </row>
     <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="10">
@@ -13688,14 +13745,14 @@
       </c>
       <c r="H123" s="10"/>
       <c r="I123" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K123" s="10"/>
       <c r="L123" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M123" s="10"/>
@@ -13704,16 +13761,16 @@
       <c r="P123" s="10"/>
       <c r="Q123" s="10"/>
       <c r="R123" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S123" s="12"/>
       <c r="T123" s="10" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U123" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V123" s="10"/>
@@ -13727,7 +13784,10 @@
       <c r="AD123" s="10"/>
       <c r="AE123" s="10"/>
       <c r="AF123" s="10"/>
-      <c r="AG123" s="10"/>
+      <c r="AG123" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1"/>
@@ -13741,10 +13801,10 @@
     </row>
     <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
@@ -13763,14 +13823,14 @@
         <v>40</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J124" s="1"/>
       <c r="K124" s="1">
         <v>27</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-31</v>
       </c>
       <c r="M124" s="1"/>
@@ -13783,18 +13843,18 @@
         <v>0</v>
       </c>
       <c r="R124" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>-0.8</v>
       </c>
       <c r="S124" s="5">
         <v>20</v>
       </c>
       <c r="T124" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>-95</v>
       </c>
       <c r="U124" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>-70</v>
       </c>
       <c r="V124" s="1">
@@ -13829,7 +13889,7 @@
       </c>
       <c r="AF124" s="1"/>
       <c r="AG124" s="1">
-        <f>G124*S124</f>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
       <c r="AH124" s="1"/>
@@ -13845,10 +13905,10 @@
     </row>
     <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -13865,14 +13925,14 @@
         <v>40</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J125" s="1"/>
       <c r="K125" s="1">
         <v>40</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-17</v>
       </c>
       <c r="M125" s="1"/>
@@ -13885,19 +13945,19 @@
         <v>10</v>
       </c>
       <c r="R125" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="S125" s="5">
-        <f t="shared" ref="S124:S128" si="40">12*R125-Q125-P125-O125-F125</f>
+        <f t="shared" ref="S125:S128" si="35">12*R125-Q125-P125-O125-F125</f>
         <v>45.199999999999996</v>
       </c>
       <c r="T125" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>12</v>
       </c>
       <c r="U125" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>2.1739130434782612</v>
       </c>
       <c r="V125" s="1">
@@ -13932,8 +13992,8 @@
       </c>
       <c r="AF125" s="1"/>
       <c r="AG125" s="1">
-        <f>G125*S125</f>
-        <v>13.559999999999999</v>
+        <f t="shared" si="24"/>
+        <v>14</v>
       </c>
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
@@ -13948,10 +14008,10 @@
     </row>
     <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C126" s="1">
         <v>226.91300000000001</v>
@@ -13972,14 +14032,14 @@
         <v>50</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J126" s="1"/>
       <c r="K126" s="1">
         <v>236.05</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>6.7239999999999895</v>
       </c>
       <c r="M126" s="1"/>
@@ -13992,16 +14052,16 @@
         <v>71.43599500000002</v>
       </c>
       <c r="R126" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>48.5548</v>
       </c>
       <c r="S126" s="5"/>
       <c r="T126" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>14.691622558428829</v>
       </c>
       <c r="U126" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>14.691622558428829</v>
       </c>
       <c r="V126" s="1">
@@ -14036,7 +14096,7 @@
       </c>
       <c r="AF126" s="1"/>
       <c r="AG126" s="1">
-        <f>G126*S126</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AH126" s="1"/>
@@ -14052,10 +14112,10 @@
     </row>
     <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C127" s="1">
         <v>-6</v>
@@ -14072,12 +14132,12 @@
         <v>40</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M127" s="1"/>
@@ -14090,18 +14150,18 @@
         <v>0</v>
       </c>
       <c r="R127" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S127" s="5">
         <v>10</v>
       </c>
       <c r="T127" s="1" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U127" s="1" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V127" s="1">
@@ -14136,7 +14196,7 @@
       </c>
       <c r="AF127" s="1"/>
       <c r="AG127" s="1">
-        <f>G127*S127</f>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="AH127" s="1"/>
@@ -14152,10 +14212,10 @@
     </row>
     <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C128" s="1">
         <v>78</v>
@@ -14176,14 +14236,14 @@
         <v>45</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J128" s="1"/>
       <c r="K128" s="1">
         <v>90</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-6</v>
       </c>
       <c r="M128" s="1"/>
@@ -14196,19 +14256,19 @@
         <v>47.53</v>
       </c>
       <c r="R128" s="1">
+        <f t="shared" si="31"/>
+        <v>16.8</v>
+      </c>
+      <c r="S128" s="5">
         <f t="shared" si="35"/>
-        <v>16.8</v>
-      </c>
-      <c r="S128" s="5">
-        <f t="shared" si="40"/>
         <v>57.57000000000005</v>
       </c>
       <c r="T128" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>12</v>
       </c>
       <c r="U128" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>8.5732142857142843</v>
       </c>
       <c r="V128" s="1">
@@ -14243,8 +14303,8 @@
       </c>
       <c r="AF128" s="1"/>
       <c r="AG128" s="1">
-        <f>G128*S128</f>
-        <v>6.9084000000000056</v>
+        <f t="shared" si="24"/>
+        <v>7</v>
       </c>
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
@@ -14259,10 +14319,10 @@
     </row>
     <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C129" s="10">
         <v>61</v>
@@ -14281,16 +14341,16 @@
       </c>
       <c r="H129" s="10"/>
       <c r="I129" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K129" s="10">
         <v>98</v>
       </c>
       <c r="L129" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>-1</v>
       </c>
       <c r="M129" s="10"/>
@@ -14303,16 +14363,16 @@
         <v>0</v>
       </c>
       <c r="R129" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="31"/>
         <v>19.399999999999999</v>
       </c>
       <c r="S129" s="12"/>
       <c r="T129" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>2.525773195876289</v>
       </c>
       <c r="U129" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>2.525773195876289</v>
       </c>
       <c r="V129" s="10">
@@ -14346,7 +14406,10 @@
         <v>0</v>
       </c>
       <c r="AF129" s="10"/>
-      <c r="AG129" s="10"/>
+      <c r="AG129" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1"/>
